--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/171.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/171.xlsx
@@ -426,13 +426,13 @@
         <v>-14.26557497487609</v>
       </c>
       <c r="E2">
-        <v>-8.354162625375931</v>
+        <v>-9.98474384673982</v>
       </c>
       <c r="F2">
-        <v>-2.561462091203486</v>
+        <v>-1.928744300168987</v>
       </c>
       <c r="G2">
-        <v>-6.65815047597731</v>
+        <v>-7.736365363208082</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.24035317422654</v>
       </c>
       <c r="E3">
-        <v>-8.864263523021943</v>
+        <v>-10.30247516854</v>
       </c>
       <c r="F3">
-        <v>-2.023697570449686</v>
+        <v>-2.120605787800992</v>
       </c>
       <c r="G3">
-        <v>-6.130343579560225</v>
+        <v>-7.671422391364199</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.08471411685993</v>
       </c>
       <c r="E4">
-        <v>-9.052788424435267</v>
+        <v>-10.34247970792375</v>
       </c>
       <c r="F4">
-        <v>-2.420949442136217</v>
+        <v>-2.117354445745004</v>
       </c>
       <c r="G4">
-        <v>-6.619897122271031</v>
+        <v>-6.983871741040662</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.79264684658436</v>
       </c>
       <c r="E5">
-        <v>-11.30739789253014</v>
+        <v>-12.27395085625329</v>
       </c>
       <c r="F5">
-        <v>-2.458829026731433</v>
+        <v>-1.725481991972253</v>
       </c>
       <c r="G5">
-        <v>-6.769778761015995</v>
+        <v>-7.585960658267913</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.37390947695603</v>
       </c>
       <c r="E6">
-        <v>-11.41698243504175</v>
+        <v>-11.98936796418926</v>
       </c>
       <c r="F6">
-        <v>-2.181148676169399</v>
+        <v>-1.817739754724242</v>
       </c>
       <c r="G6">
-        <v>-6.082473091062364</v>
+        <v>-7.867661599295577</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.85490729777512</v>
       </c>
       <c r="E7">
-        <v>-11.79003359531963</v>
+        <v>-12.48457923929806</v>
       </c>
       <c r="F7">
-        <v>-2.278248246390752</v>
+        <v>-1.680347565663319</v>
       </c>
       <c r="G7">
-        <v>-6.162515461110863</v>
+        <v>-7.179127716946877</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.26245244491761</v>
       </c>
       <c r="E8">
-        <v>-12.45354107844948</v>
+        <v>-13.12660817020953</v>
       </c>
       <c r="F8">
-        <v>-1.525758469320278</v>
+        <v>-1.852174159291215</v>
       </c>
       <c r="G8">
-        <v>-5.796673694657083</v>
+        <v>-6.579117822318288</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.6120899008215</v>
       </c>
       <c r="E9">
-        <v>-13.71747893025635</v>
+        <v>-14.96075788364022</v>
       </c>
       <c r="F9">
-        <v>-1.994442118885016</v>
+        <v>-1.742133833503329</v>
       </c>
       <c r="G9">
-        <v>-4.997339163654515</v>
+        <v>-6.720507911755022</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.9218346694965</v>
       </c>
       <c r="E10">
-        <v>-13.84996849429876</v>
+        <v>-15.70298835891942</v>
       </c>
       <c r="F10">
-        <v>-1.727282862705939</v>
+        <v>-1.796121850613383</v>
       </c>
       <c r="G10">
-        <v>-4.477083621612509</v>
+        <v>-5.673640580235609</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.21808224134901</v>
       </c>
       <c r="E11">
-        <v>-15.12237459249997</v>
+        <v>-16.51901484662761</v>
       </c>
       <c r="F11">
-        <v>-2.24423713756661</v>
+        <v>-1.509997122747212</v>
       </c>
       <c r="G11">
-        <v>-4.337325631126637</v>
+        <v>-5.008383143573524</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.513634436740034</v>
       </c>
       <c r="E12">
-        <v>-15.45218788295261</v>
+        <v>-16.90328303702248</v>
       </c>
       <c r="F12">
-        <v>-1.776410019896366</v>
+        <v>-1.711662338591349</v>
       </c>
       <c r="G12">
-        <v>-3.256058420908657</v>
+        <v>-4.906891748976087</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.810047926710221</v>
       </c>
       <c r="E13">
-        <v>-17.04771871549713</v>
+        <v>-17.95269801813799</v>
       </c>
       <c r="F13">
-        <v>-2.253772474740235</v>
+        <v>-1.559478821186038</v>
       </c>
       <c r="G13">
-        <v>-3.573635743945402</v>
+        <v>-4.333687341578978</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.1304953779462</v>
       </c>
       <c r="E14">
-        <v>-16.96756019708736</v>
+        <v>-18.38575598749151</v>
       </c>
       <c r="F14">
-        <v>-2.101487896511782</v>
+        <v>-1.39647848223497</v>
       </c>
       <c r="G14">
-        <v>-2.158953560830803</v>
+        <v>-4.156473838861791</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.482265724677082</v>
       </c>
       <c r="E15">
-        <v>-18.84175520616788</v>
+        <v>-19.39167497576334</v>
       </c>
       <c r="F15">
-        <v>-2.019528397311396</v>
+        <v>-1.155494807616955</v>
       </c>
       <c r="G15">
-        <v>-1.562436291746146</v>
+        <v>-3.01116081464107</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.864223380583313</v>
       </c>
       <c r="E16">
-        <v>-17.8169751236541</v>
+        <v>-19.98545754459709</v>
       </c>
       <c r="F16">
-        <v>-1.598348304827599</v>
+        <v>-0.9977206386101499</v>
       </c>
       <c r="G16">
-        <v>-1.614044386157844</v>
+        <v>-2.497582642951774</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.285736094982968</v>
       </c>
       <c r="E17">
-        <v>-19.64515177986868</v>
+        <v>-20.26665313810338</v>
       </c>
       <c r="F17">
-        <v>-1.637345357049191</v>
+        <v>-1.143964761737389</v>
       </c>
       <c r="G17">
-        <v>-0.02812423502444265</v>
+        <v>-1.728086058894658</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.752543568537454</v>
       </c>
       <c r="E18">
-        <v>-20.28293300216096</v>
+        <v>-21.18219284213013</v>
       </c>
       <c r="F18">
-        <v>-1.026916447721818</v>
+        <v>-1.33184842910115</v>
       </c>
       <c r="G18">
-        <v>-0.3734869667722914</v>
+        <v>-1.300462891586999</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.260703221883548</v>
       </c>
       <c r="E19">
-        <v>-20.7696715024014</v>
+        <v>-22.70158191270968</v>
       </c>
       <c r="F19">
-        <v>-1.373604773141468</v>
+        <v>-0.9410230317255377</v>
       </c>
       <c r="G19">
-        <v>0.7680851409890528</v>
+        <v>-1.505627330292252</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.805566557935929</v>
       </c>
       <c r="E20">
-        <v>-22.17283728757409</v>
+        <v>-21.94669888105305</v>
       </c>
       <c r="F20">
-        <v>-0.9108306966283014</v>
+        <v>-1.224784427391522</v>
       </c>
       <c r="G20">
-        <v>1.419050952558103</v>
+        <v>-0.1997031892337897</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.393090748285652</v>
       </c>
       <c r="E21">
-        <v>-22.28976701492615</v>
+        <v>-24.16423373244713</v>
       </c>
       <c r="F21">
-        <v>-1.003133191220042</v>
+        <v>-0.5743967312879074</v>
       </c>
       <c r="G21">
-        <v>2.63320015017689</v>
+        <v>0.001064844995311408</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.021496843881005</v>
       </c>
       <c r="E22">
-        <v>-22.38333434487263</v>
+        <v>-24.49811812103266</v>
       </c>
       <c r="F22">
-        <v>-1.101524186222359</v>
+        <v>-0.4645494151048733</v>
       </c>
       <c r="G22">
-        <v>1.23610027442136</v>
+        <v>0.2934952641157532</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.685614133191466</v>
       </c>
       <c r="E23">
-        <v>-23.15769434323624</v>
+        <v>-24.20317408043908</v>
       </c>
       <c r="F23">
-        <v>-1.126201251151756</v>
+        <v>-0.281292179685747</v>
       </c>
       <c r="G23">
-        <v>1.897252634614748</v>
+        <v>0.3252003587453534</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.395684771930558</v>
       </c>
       <c r="E24">
-        <v>-24.32370847310125</v>
+        <v>-24.89130740522265</v>
       </c>
       <c r="F24">
-        <v>-0.3109104561728434</v>
+        <v>-0.5155296301753632</v>
       </c>
       <c r="G24">
-        <v>1.773795770364247</v>
+        <v>0.5280076890266455</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.157205823390115</v>
       </c>
       <c r="E25">
-        <v>-24.8004752735768</v>
+        <v>-25.69501644362998</v>
       </c>
       <c r="F25">
-        <v>-0.3763721901790743</v>
+        <v>-0.2232774686306837</v>
       </c>
       <c r="G25">
-        <v>1.276138012173305</v>
+        <v>0.4774953851884458</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.972913132173808</v>
       </c>
       <c r="E26">
-        <v>-24.46365190536028</v>
+        <v>-25.87237865661439</v>
       </c>
       <c r="F26">
-        <v>-0.3706514848953409</v>
+        <v>-0.3075381724760466</v>
       </c>
       <c r="G26">
-        <v>2.684066682387792</v>
+        <v>0.6557947468425134</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.850560666773744</v>
       </c>
       <c r="E27">
-        <v>-24.43364170811145</v>
+        <v>-25.94727055975325</v>
       </c>
       <c r="F27">
-        <v>-0.3958959814956559</v>
+        <v>-0.2032243505437133</v>
       </c>
       <c r="G27">
-        <v>2.428118475110118</v>
+        <v>0.7776327543243109</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.80067183562359</v>
       </c>
       <c r="E28">
-        <v>-25.46101660623163</v>
+        <v>-25.20579181115933</v>
       </c>
       <c r="F28">
-        <v>-0.6082603907143511</v>
+        <v>-0.5361369260548066</v>
       </c>
       <c r="G28">
-        <v>1.985475362690786</v>
+        <v>0.3107167220110419</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.826366312118361</v>
       </c>
       <c r="E29">
-        <v>-24.48788376977533</v>
+        <v>-24.47148616539355</v>
       </c>
       <c r="F29">
-        <v>-0.1372018118057871</v>
+        <v>0.03951380623343147</v>
       </c>
       <c r="G29">
-        <v>2.887612264324341</v>
+        <v>0.4534839983921118</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.923144251318473</v>
       </c>
       <c r="E30">
-        <v>-23.61166480555718</v>
+        <v>-25.12880322455492</v>
       </c>
       <c r="F30">
-        <v>-0.1700109595284671</v>
+        <v>-0.1355782116963</v>
       </c>
       <c r="G30">
-        <v>1.782376704402038</v>
+        <v>0.7555679683050683</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.094916617223098</v>
       </c>
       <c r="E31">
-        <v>-23.89483934220483</v>
+        <v>-25.4483097081661</v>
       </c>
       <c r="F31">
-        <v>0.1144255555707992</v>
+        <v>-0.1358830509005303</v>
       </c>
       <c r="G31">
-        <v>0.7787517187165846</v>
+        <v>0.4596581658228526</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.33659504491996</v>
       </c>
       <c r="E32">
-        <v>-24.49872493654969</v>
+        <v>-24.12272573969282</v>
       </c>
       <c r="F32">
-        <v>-0.2653833837149825</v>
+        <v>-0.008475174145549495</v>
       </c>
       <c r="G32">
-        <v>1.316440593568393</v>
+        <v>0.03079354393796667</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.634132332127731</v>
       </c>
       <c r="E33">
-        <v>-23.67337884933372</v>
+        <v>-23.93825835099037</v>
       </c>
       <c r="F33">
-        <v>-0.307503381045129</v>
+        <v>-0.1190075501706987</v>
       </c>
       <c r="G33">
-        <v>1.7502975181265</v>
+        <v>-0.4994532245415601</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.977824267563426</v>
       </c>
       <c r="E34">
-        <v>-22.6669979567131</v>
+        <v>-23.38837480918697</v>
       </c>
       <c r="F34">
-        <v>-0.5355960021407785</v>
+        <v>-0.3374190414298304</v>
       </c>
       <c r="G34">
-        <v>0.9780035230886994</v>
+        <v>0.1684592696430197</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.354955466024434</v>
       </c>
       <c r="E35">
-        <v>-23.31215606316387</v>
+        <v>-23.04294281188188</v>
       </c>
       <c r="F35">
-        <v>-0.1323889971955219</v>
+        <v>-0.1953200687862004</v>
       </c>
       <c r="G35">
-        <v>-1.069790699501661</v>
+        <v>0.09939466860274421</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.747221465366324</v>
       </c>
       <c r="E36">
-        <v>-20.77332598092559</v>
+        <v>-22.57061844440785</v>
       </c>
       <c r="F36">
-        <v>-0.1673825497593842</v>
+        <v>-0.06070788072907232</v>
       </c>
       <c r="G36">
-        <v>1.352710930496648</v>
+        <v>-1.362257534623035</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.135743634840894</v>
       </c>
       <c r="E37">
-        <v>-21.61479343560887</v>
+        <v>-22.31560648761391</v>
       </c>
       <c r="F37">
-        <v>-0.08802246746898322</v>
+        <v>-0.2759773744293855</v>
       </c>
       <c r="G37">
-        <v>0.05169301792738567</v>
+        <v>-1.241886098815134</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.511055886029826</v>
       </c>
       <c r="E38">
-        <v>-21.03118634787035</v>
+        <v>-22.38601972995918</v>
       </c>
       <c r="F38">
-        <v>-0.1753406753980791</v>
+        <v>-0.07169451759240217</v>
       </c>
       <c r="G38">
-        <v>-0.1360546406957619</v>
+        <v>-1.855714210524641</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.862754897613552</v>
       </c>
       <c r="E39">
-        <v>-20.64875218944858</v>
+        <v>-20.10595570946719</v>
       </c>
       <c r="F39">
-        <v>-0.03552302658175895</v>
+        <v>-0.233543425853578</v>
       </c>
       <c r="G39">
-        <v>-0.1093186749206078</v>
+        <v>-1.164472301924817</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.176735456090507</v>
       </c>
       <c r="E40">
-        <v>-20.68610757153786</v>
+        <v>-21.15612694574198</v>
       </c>
       <c r="F40">
-        <v>-0.5567400800972359</v>
+        <v>0.02007202328972707</v>
       </c>
       <c r="G40">
-        <v>-0.87742482985123</v>
+        <v>-1.593618320180541</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.453102523234539</v>
       </c>
       <c r="E41">
-        <v>-17.3714683792535</v>
+        <v>-20.27873963522985</v>
       </c>
       <c r="F41">
-        <v>0.2602571517314437</v>
+        <v>0.1172420047403175</v>
       </c>
       <c r="G41">
-        <v>-0.711242064870895</v>
+        <v>-1.440164602798704</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.69184747045241</v>
       </c>
       <c r="E42">
-        <v>-17.8805005570337</v>
+        <v>-19.23905634475683</v>
       </c>
       <c r="F42">
-        <v>-0.4815036107379708</v>
+        <v>-0.1158895752665614</v>
       </c>
       <c r="G42">
-        <v>-0.7711000387664574</v>
+        <v>-1.690845732123396</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.890037313029969</v>
       </c>
       <c r="E43">
-        <v>-17.35583608697902</v>
+        <v>-18.24956666018483</v>
       </c>
       <c r="F43">
-        <v>-0.5508860076616517</v>
+        <v>0.19881879820061</v>
       </c>
       <c r="G43">
-        <v>-1.318349769135681</v>
+        <v>-2.040687631985879</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.049805112165063</v>
       </c>
       <c r="E44">
-        <v>-17.41082987532817</v>
+        <v>-17.27180119481868</v>
       </c>
       <c r="F44">
-        <v>0.3613859010000129</v>
+        <v>0.3199907251473161</v>
       </c>
       <c r="G44">
-        <v>-1.36877599878986</v>
+        <v>-2.446831979834747</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.177690587000447</v>
       </c>
       <c r="E45">
-        <v>-15.39617518795174</v>
+        <v>-17.37417640671009</v>
       </c>
       <c r="F45">
-        <v>0.4344520477639434</v>
+        <v>0.271609926986811</v>
       </c>
       <c r="G45">
-        <v>-0.6850854445651133</v>
+        <v>-2.021555989314431</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.274627526078868</v>
       </c>
       <c r="E46">
-        <v>-15.32531815515372</v>
+        <v>-15.81688853716034</v>
       </c>
       <c r="F46">
-        <v>0.9067432373678731</v>
+        <v>0.6468628455571954</v>
       </c>
       <c r="G46">
-        <v>-2.086541998250324</v>
+        <v>-3.233907560705393</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.338217037000174</v>
       </c>
       <c r="E47">
-        <v>-13.4626390554747</v>
+        <v>-15.42586839202003</v>
       </c>
       <c r="F47">
-        <v>0.4261352390398363</v>
+        <v>0.4968206578881209</v>
       </c>
       <c r="G47">
-        <v>-1.292981058668246</v>
+        <v>-2.882728200445045</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.373698749230023</v>
       </c>
       <c r="E48">
-        <v>-15.01574714351536</v>
+        <v>-15.70183359804746</v>
       </c>
       <c r="F48">
-        <v>0.550283490064801</v>
+        <v>0.5098881536672831</v>
       </c>
       <c r="G48">
-        <v>-1.724795376628622</v>
+        <v>-4.463324994351298</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.380979520693319</v>
       </c>
       <c r="E49">
-        <v>-13.18274766248262</v>
+        <v>-13.73377237973595</v>
       </c>
       <c r="F49">
-        <v>0.517247369673754</v>
+        <v>0.276559422218538</v>
       </c>
       <c r="G49">
-        <v>-1.939427975576191</v>
+        <v>-4.186315096352781</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.35204553602664</v>
       </c>
       <c r="E50">
-        <v>-11.58655567273298</v>
+        <v>-14.06933683217833</v>
       </c>
       <c r="F50">
-        <v>0.1395002368535402</v>
+        <v>0.7076153108785112</v>
       </c>
       <c r="G50">
-        <v>-2.684694676831382</v>
+        <v>-4.046808707327894</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.289076062778638</v>
       </c>
       <c r="E51">
-        <v>-13.05643946546068</v>
+        <v>-12.46334069620208</v>
       </c>
       <c r="F51">
-        <v>0.8410851802871787</v>
+        <v>0.4705489857083346</v>
       </c>
       <c r="G51">
-        <v>-2.899436523781747</v>
+        <v>-4.03319905461595</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.190116987788668</v>
       </c>
       <c r="E52">
-        <v>-10.46546853349807</v>
+        <v>-11.74825842259887</v>
       </c>
       <c r="F52">
-        <v>0.7597991437852688</v>
+        <v>0.7731988148929536</v>
       </c>
       <c r="G52">
-        <v>-3.594118089196873</v>
+        <v>-4.348025314309561</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.048081551791166</v>
       </c>
       <c r="E53">
-        <v>-11.26141576745625</v>
+        <v>-10.9118719157522</v>
       </c>
       <c r="F53">
-        <v>0.9352589568418432</v>
+        <v>0.4577962695422362</v>
       </c>
       <c r="G53">
-        <v>-3.933068294235154</v>
+        <v>-3.636350718641356</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.862636698197297</v>
       </c>
       <c r="E54">
-        <v>-9.748900920420347</v>
+        <v>-10.94269723832241</v>
       </c>
       <c r="F54">
-        <v>0.4304841679045337</v>
+        <v>0.3108405788159928</v>
       </c>
       <c r="G54">
-        <v>-3.147333484307912</v>
+        <v>-4.265745015476515</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.636316469088051</v>
       </c>
       <c r="E55">
-        <v>-8.591581460650072</v>
+        <v>-10.15663566312297</v>
       </c>
       <c r="F55">
-        <v>0.8020177168363484</v>
+        <v>0.5049096655764581</v>
       </c>
       <c r="G55">
-        <v>-4.213627097051769</v>
+        <v>-4.708606623901439</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.367586377762948</v>
       </c>
       <c r="E56">
-        <v>-8.903520864194437</v>
+        <v>-9.523631980908785</v>
       </c>
       <c r="F56">
-        <v>0.5431512467266972</v>
+        <v>0.4238870499086385</v>
       </c>
       <c r="G56">
-        <v>-4.30878210748704</v>
+        <v>-5.004317793651299</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.055084063489847</v>
       </c>
       <c r="E57">
-        <v>-8.66770510871901</v>
+        <v>-9.757622761359121</v>
       </c>
       <c r="F57">
-        <v>1.017075148481545</v>
+        <v>0.5149710160508609</v>
       </c>
       <c r="G57">
-        <v>-5.793346596390116</v>
+        <v>-4.75516613636575</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.706868666542385</v>
       </c>
       <c r="E58">
-        <v>-7.012176524046867</v>
+        <v>-7.902755279343334</v>
       </c>
       <c r="F58">
-        <v>0.09304787800675232</v>
+        <v>0.5805843412918041</v>
       </c>
       <c r="G58">
-        <v>-4.528529499292784</v>
+        <v>-5.233784947160342</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.325433797107173</v>
       </c>
       <c r="E59">
-        <v>-6.229656215521429</v>
+        <v>-8.738661767945198</v>
       </c>
       <c r="F59">
-        <v>-0.01285723770635888</v>
+        <v>0.6133744365642197</v>
       </c>
       <c r="G59">
-        <v>-4.683827190539994</v>
+        <v>-4.926169055651264</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.910671933177922</v>
       </c>
       <c r="E60">
-        <v>-5.777085051668861</v>
+        <v>-8.070892990774126</v>
       </c>
       <c r="F60">
-        <v>0.1312099358863227</v>
+        <v>0.5247101316055747</v>
       </c>
       <c r="G60">
-        <v>-4.618268457225807</v>
+        <v>-6.121676571338414</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.472418471890686</v>
       </c>
       <c r="E61">
-        <v>-4.502460001203893</v>
+        <v>-8.356272894263505</v>
       </c>
       <c r="F61">
-        <v>0.1598159474071981</v>
+        <v>0.2666836260423623</v>
       </c>
       <c r="G61">
-        <v>-3.601616474843322</v>
+        <v>-5.713204909975438</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.014799507390873</v>
       </c>
       <c r="E62">
-        <v>-5.556018536036417</v>
+        <v>-7.570464913608499</v>
       </c>
       <c r="F62">
-        <v>0.4831302298220535</v>
+        <v>0.4994962845991633</v>
       </c>
       <c r="G62">
-        <v>-4.70079373642876</v>
+        <v>-5.943618879508713</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.538945699714915</v>
       </c>
       <c r="E63">
-        <v>-6.287335388957127</v>
+        <v>-7.767299564825898</v>
       </c>
       <c r="F63">
-        <v>0.543764238604769</v>
+        <v>0.1374384303879722</v>
       </c>
       <c r="G63">
-        <v>-3.270012370356684</v>
+        <v>-5.523980748041776</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.051342509492772</v>
       </c>
       <c r="E64">
-        <v>-5.56858957988171</v>
+        <v>-6.943832794323106</v>
       </c>
       <c r="F64">
-        <v>0.3410180032999787</v>
+        <v>0.3385345578263858</v>
       </c>
       <c r="G64">
-        <v>-4.59345591840897</v>
+        <v>-5.586937392562096</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.55635237762025</v>
       </c>
       <c r="E65">
-        <v>-5.547378207629782</v>
+        <v>-7.164799683527381</v>
       </c>
       <c r="F65">
-        <v>0.2125208234103166</v>
+        <v>0.5622625110766847</v>
       </c>
       <c r="G65">
-        <v>-5.541092957934269</v>
+        <v>-5.766968169533203</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.053872359741753</v>
       </c>
       <c r="E66">
-        <v>-5.901753941100026</v>
+        <v>-7.673532982023076</v>
       </c>
       <c r="F66">
-        <v>0.2674622914009938</v>
+        <v>0.08512371543157224</v>
       </c>
       <c r="G66">
-        <v>-4.154990714460197</v>
+        <v>-5.148607920980433</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.545622913520392</v>
       </c>
       <c r="E67">
-        <v>-3.84632034528452</v>
+        <v>-6.519637048602601</v>
       </c>
       <c r="F67">
-        <v>0.08408162923885047</v>
+        <v>-0.04058103794325273</v>
       </c>
       <c r="G67">
-        <v>-4.357400779276777</v>
+        <v>-5.648791625417839</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.03586567228982</v>
       </c>
       <c r="E68">
-        <v>-4.677884027313027</v>
+        <v>-6.711970396656375</v>
       </c>
       <c r="F68">
-        <v>0.03673877543405312</v>
+        <v>-0.2605506882870502</v>
       </c>
       <c r="G68">
-        <v>-4.759397013564938</v>
+        <v>-5.236122192311067</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.5238212893318513</v>
       </c>
       <c r="E69">
-        <v>-5.461944017001073</v>
+        <v>-6.756734362222197</v>
       </c>
       <c r="F69">
-        <v>0.1983764500075151</v>
+        <v>0.2787082072613999</v>
       </c>
       <c r="G69">
-        <v>-3.531409735591998</v>
+        <v>-4.746734176877226</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.009276144786878051</v>
       </c>
       <c r="E70">
-        <v>-3.740969925970076</v>
+        <v>-6.838563887540801</v>
       </c>
       <c r="F70">
-        <v>0.00649756666005157</v>
+        <v>-0.05507829585964688</v>
       </c>
       <c r="G70">
-        <v>-3.665533177570031</v>
+        <v>-5.264109544300066</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.5026810334684338</v>
       </c>
       <c r="E71">
-        <v>-3.129743675258778</v>
+        <v>-6.117757622791895</v>
       </c>
       <c r="F71">
-        <v>0.2024735551817614</v>
+        <v>0.1292616157549383</v>
       </c>
       <c r="G71">
-        <v>-4.341268490863909</v>
+        <v>-4.650854156968854</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.012524326472472</v>
       </c>
       <c r="E72">
-        <v>-6.082480810272142</v>
+        <v>-6.645804862930304</v>
       </c>
       <c r="F72">
-        <v>-0.3034543211802451</v>
+        <v>-0.102843617039872</v>
       </c>
       <c r="G72">
-        <v>-3.37595975924998</v>
+        <v>-4.998530960048653</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.520024193161316</v>
       </c>
       <c r="E73">
-        <v>-5.311843217542831</v>
+        <v>-6.432278256520632</v>
       </c>
       <c r="F73">
-        <v>-0.1335139201285237</v>
+        <v>-0.1336058689102344</v>
       </c>
       <c r="G73">
-        <v>-3.366640573556932</v>
+        <v>-5.110397604366166</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.018413145559921</v>
       </c>
       <c r="E74">
-        <v>-4.997440324138294</v>
+        <v>-7.38169547459876</v>
       </c>
       <c r="F74">
-        <v>-0.2113050745580224</v>
+        <v>-0.272372319492402</v>
       </c>
       <c r="G74">
-        <v>-2.944075919833279</v>
+        <v>-3.389867361060459</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.505888089149217</v>
       </c>
       <c r="E75">
-        <v>-5.268292883011066</v>
+        <v>-7.638305982717409</v>
       </c>
       <c r="F75">
-        <v>-0.3133748491961719</v>
+        <v>-0.3728855917806912</v>
       </c>
       <c r="G75">
-        <v>-3.137977882613932</v>
+        <v>-3.587622798848823</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.980105166594245</v>
       </c>
       <c r="E76">
-        <v>-6.384317188305395</v>
+        <v>-8.346686114789268</v>
       </c>
       <c r="F76">
-        <v>-0.07359396404702143</v>
+        <v>-0.3689616153936299</v>
       </c>
       <c r="G76">
-        <v>-2.256571617147292</v>
+        <v>-3.533257020002912</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.433484543248879</v>
       </c>
       <c r="E77">
-        <v>-7.119533057346707</v>
+        <v>-8.043731203676121</v>
       </c>
       <c r="F77">
-        <v>-0.8645067347289473</v>
+        <v>-0.6079224168140089</v>
       </c>
       <c r="G77">
-        <v>-2.536094219210116</v>
+        <v>-3.626918974399972</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.861900825161252</v>
       </c>
       <c r="E78">
-        <v>-8.00771172141911</v>
+        <v>-8.514606459467691</v>
       </c>
       <c r="F78">
-        <v>-0.886624972751097</v>
+        <v>-0.4897516649676454</v>
       </c>
       <c r="G78">
-        <v>-1.31499287595886</v>
+        <v>-2.903594568979071</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.264100909351824</v>
       </c>
       <c r="E79">
-        <v>-8.695138604257478</v>
+        <v>-10.25643870177802</v>
       </c>
       <c r="F79">
-        <v>-0.4208662884856442</v>
+        <v>-0.7518355140697699</v>
       </c>
       <c r="G79">
-        <v>-2.196064776326033</v>
+        <v>-2.752925020395761</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>4.636234608232808</v>
       </c>
       <c r="E80">
-        <v>-7.545141686957606</v>
+        <v>-10.06894629243844</v>
       </c>
       <c r="F80">
-        <v>-0.9921772039506156</v>
+        <v>-0.473090711395139</v>
       </c>
       <c r="G80">
-        <v>-0.7699181740089376</v>
+        <v>-2.55461010041126</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>4.976844101915307</v>
       </c>
       <c r="E81">
-        <v>-8.806362454359871</v>
+        <v>-10.32111889602957</v>
       </c>
       <c r="F81">
-        <v>-0.8914129363392781</v>
+        <v>-0.446958204939023</v>
       </c>
       <c r="G81">
-        <v>-0.2063309014034106</v>
+        <v>-1.408939537272298</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>5.2895060883971</v>
       </c>
       <c r="E82">
-        <v>-10.44129101077112</v>
+        <v>-11.44288530636563</v>
       </c>
       <c r="F82">
-        <v>-0.8254119351538247</v>
+        <v>-0.8889543418877692</v>
       </c>
       <c r="G82">
-        <v>0.1139114107924484</v>
+        <v>-1.857657500756193</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>5.576988101826206</v>
       </c>
       <c r="E83">
-        <v>-11.72617758333747</v>
+        <v>-12.23147377006135</v>
       </c>
       <c r="F83">
-        <v>-1.180560376858265</v>
+        <v>-0.8027627136264807</v>
       </c>
       <c r="G83">
-        <v>0.02088839168446728</v>
+        <v>-0.5411230612443665</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>5.837289410537206</v>
       </c>
       <c r="E84">
-        <v>-12.52017757347235</v>
+        <v>-13.28663538469258</v>
       </c>
       <c r="F84">
-        <v>-1.029375042173327</v>
+        <v>-1.108312657088301</v>
       </c>
       <c r="G84">
-        <v>0.1944669153995341</v>
+        <v>-1.191873687353364</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>6.075878813489128</v>
       </c>
       <c r="E85">
-        <v>-13.69490901580212</v>
+        <v>-14.9450395503596</v>
       </c>
       <c r="F85">
-        <v>-1.001353029671426</v>
+        <v>-1.121936815762144</v>
       </c>
       <c r="G85">
-        <v>0.4045971724136942</v>
+        <v>-0.5283741503726331</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>6.2950521534593</v>
       </c>
       <c r="E86">
-        <v>-12.26905104737699</v>
+        <v>-14.82810982300754</v>
       </c>
       <c r="F86">
-        <v>-1.105378579747585</v>
+        <v>-1.364689883152539</v>
       </c>
       <c r="G86">
-        <v>1.193692186063296</v>
+        <v>-0.5374582873323933</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>6.488721534812205</v>
       </c>
       <c r="E87">
-        <v>-14.30599488381918</v>
+        <v>-15.79368010787103</v>
       </c>
       <c r="F87">
-        <v>-1.797396708046292</v>
+        <v>-1.545346873294278</v>
       </c>
       <c r="G87">
-        <v>1.803017955839394</v>
+        <v>-0.1788202679720671</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>6.656922298655193</v>
       </c>
       <c r="E88">
-        <v>-15.79507487786539</v>
+        <v>-16.77648576480771</v>
       </c>
       <c r="F88">
-        <v>-1.0533347409319</v>
+        <v>-1.126263378706966</v>
       </c>
       <c r="G88">
-        <v>0.990914650691857</v>
+        <v>0.04785940619290964</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>6.796465622096814</v>
       </c>
       <c r="E89">
-        <v>-17.56267413727937</v>
+        <v>-18.93609237669567</v>
       </c>
       <c r="F89">
-        <v>-1.86695886069638</v>
+        <v>-1.460277682863783</v>
       </c>
       <c r="G89">
-        <v>1.56833007201492</v>
+        <v>-0.2280547012321082</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>6.898048411047086</v>
       </c>
       <c r="E90">
-        <v>-17.95530641916641</v>
+        <v>-20.63092811575439</v>
       </c>
       <c r="F90">
-        <v>-1.061393099026334</v>
+        <v>-1.716955606295237</v>
       </c>
       <c r="G90">
-        <v>1.379016525351697</v>
+        <v>-0.1400504691616622</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>6.954189511480093</v>
       </c>
       <c r="E91">
-        <v>-21.05570350614788</v>
+        <v>-21.80463159448442</v>
       </c>
       <c r="F91">
-        <v>-1.18738529588993</v>
+        <v>-1.45059820976207</v>
       </c>
       <c r="G91">
-        <v>1.229962522991551</v>
+        <v>-0.2367349516360772</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>6.961708679025477</v>
       </c>
       <c r="E92">
-        <v>-23.0030424274003</v>
+        <v>-23.57025191075704</v>
       </c>
       <c r="F92">
-        <v>-1.5758606149438</v>
+        <v>-1.677526146289384</v>
       </c>
       <c r="G92">
-        <v>2.629028862797408</v>
+        <v>-0.158970236918597</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.913425453570937</v>
       </c>
       <c r="E93">
-        <v>-24.48044348698073</v>
+        <v>-25.8455202772749</v>
       </c>
       <c r="F93">
-        <v>-2.040017236652239</v>
+        <v>-1.804972127944893</v>
       </c>
       <c r="G93">
-        <v>1.634633678075443</v>
+        <v>-0.12361692110472</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>6.799762406843134</v>
       </c>
       <c r="E94">
-        <v>-26.40571515439376</v>
+        <v>-27.47776797707361</v>
       </c>
       <c r="F94">
-        <v>-1.890436449626524</v>
+        <v>-1.826557725727043</v>
       </c>
       <c r="G94">
-        <v>1.162705479815717</v>
+        <v>-0.4566114547178516</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>6.625606045339631</v>
       </c>
       <c r="E95">
-        <v>-27.07864186345957</v>
+        <v>-28.99513734824574</v>
       </c>
       <c r="F95">
-        <v>-1.664917566051372</v>
+        <v>-2.144538978802675</v>
       </c>
       <c r="G95">
-        <v>0.6370438169080813</v>
+        <v>0.03249185379961279</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>6.385814613916099</v>
       </c>
       <c r="E96">
-        <v>-29.82380054267234</v>
+        <v>-31.14655647912783</v>
       </c>
       <c r="F96">
-        <v>-2.08176281191632</v>
+        <v>-1.790762313517271</v>
       </c>
       <c r="G96">
-        <v>0.8311444124210903</v>
+        <v>-1.181968535099865</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.085297704844047</v>
       </c>
       <c r="E97">
-        <v>-32.82266924240184</v>
+        <v>-33.35972588157851</v>
       </c>
       <c r="F97">
-        <v>-2.090034060433273</v>
+        <v>-2.288708041585901</v>
       </c>
       <c r="G97">
-        <v>0.6746483036886628</v>
+        <v>-0.8325073479743986</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.717979611243226</v>
       </c>
       <c r="E98">
-        <v>-35.44859772946666</v>
+        <v>-35.7477170230953</v>
       </c>
       <c r="F98">
-        <v>-2.550066240843173</v>
+        <v>-2.229110320424088</v>
       </c>
       <c r="G98">
-        <v>-0.2538405404374914</v>
+        <v>-1.496996738071372</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.314300085557438</v>
       </c>
       <c r="E99">
-        <v>-37.42701103935971</v>
+        <v>-37.39134477807529</v>
       </c>
       <c r="F99">
-        <v>-2.759073276978322</v>
+        <v>-2.306077249287801</v>
       </c>
       <c r="G99">
-        <v>0.854371199924617</v>
+        <v>-1.48637650798139</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.843835802876277</v>
       </c>
       <c r="E100">
-        <v>-39.02449590843853</v>
+        <v>-40.39224449839723</v>
       </c>
       <c r="F100">
-        <v>-2.571610420255182</v>
+        <v>-2.676785744286427</v>
       </c>
       <c r="G100">
-        <v>-0.677487742552486</v>
+        <v>-1.70813340092947</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.369685619276876</v>
       </c>
       <c r="E101">
-        <v>-40.71352614381942</v>
+        <v>-42.63751851732529</v>
       </c>
       <c r="F101">
-        <v>-2.48354751003097</v>
+        <v>-2.725503687979872</v>
       </c>
       <c r="G101">
-        <v>-0.9373092881111066</v>
+        <v>-2.316194542309566</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.810203228944602</v>
       </c>
       <c r="E102">
-        <v>-43.19671486592546</v>
+        <v>-44.20573133041854</v>
       </c>
       <c r="F102">
-        <v>-2.71452533479057</v>
+        <v>-2.737515843687868</v>
       </c>
       <c r="G102">
-        <v>-1.004467014920762</v>
+        <v>-2.287773508854923</v>
       </c>
     </row>
   </sheetData>
